--- a/data/trans_bre/P1419-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1419-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,92</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>205,7%</t>
+          <t>196,38%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,57</t>
+          <t>2,86; 7,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 9,83</t>
+          <t>4,7; 9,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,96</t>
+          <t>1,22; 5,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,07</t>
+          <t>5,13; 9,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,58; 441,84</t>
+          <t>69,79; 402,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>174,78; 995,96</t>
+          <t>177,14; 918,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,27; 584,02</t>
+          <t>44,57; 631,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94,16; 347,97</t>
+          <t>96,47; 350,92</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,55</t>
+          <t>7,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>370,55%</t>
+          <t>254,81%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,46</t>
+          <t>5,54; 10,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,99</t>
+          <t>6,19; 10,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,54</t>
+          <t>4,81; 8,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,58</t>
+          <t>5,8; 9,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>141,34; 510,46</t>
+          <t>145,36; 508,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>345,07; 1641,61</t>
+          <t>334,72; 1607,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>318,23; 1634,14</t>
+          <t>342,12; 1693,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>200,2; 837,05</t>
+          <t>138,26; 413,4</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>158,09%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,04</t>
+          <t>5,51; 11,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,14</t>
+          <t>4,65; 9,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,51</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,35</t>
+          <t>4,57; 9,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121,52; 492,15</t>
+          <t>112,59; 489,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>243,76; 1634,98</t>
+          <t>204,45; 1599,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,44; 449,33</t>
+          <t>39,77; 482,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 195,09</t>
+          <t>82,83; 277,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>6,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>121,75%</t>
+          <t>146,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,28</t>
+          <t>6,78; 11,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 8,73</t>
+          <t>5,19; 8,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 7,34</t>
+          <t>3,13; 6,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,31</t>
+          <t>4,05; 8,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>158,68; 486,38</t>
+          <t>150,33; 428,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>265,51; 1494,64</t>
+          <t>269,49; 1438,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,8; 441,35</t>
+          <t>92,29; 411,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,1; 209,7</t>
+          <t>75,45; 241,59</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>184,25%</t>
+          <t>184,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,01</t>
+          <t>6,55; 9,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,35</t>
+          <t>6,23; 8,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,66</t>
+          <t>3,68; 5,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,74</t>
+          <t>6,07; 8,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>192,27; 355,19</t>
+          <t>181,26; 357,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>415,34; 925,64</t>
+          <t>411,1; 927,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>193,28; 453,77</t>
+          <t>197,03; 452,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>125,75; 266,53</t>
+          <t>140,01; 235,56</t>
         </is>
       </c>
     </row>
